--- a/results/0916-all/兴安岭林区/tech_selected_summary.xlsx
+++ b/results/0916-all/兴安岭林区/tech_selected_summary.xlsx
@@ -121,52 +121,52 @@
     <t>扎兰屯市</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 1257823.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>1257823.56</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 944701.74</t>
+    <t>944701.74</t>
   </si>
   <si>
     <t>4R(Right place)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 18791393.45</t>
+    <t>18791393.45</t>
   </si>
   <si>
     <t>4R(Right rate)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 9218004.04</t>
+    <t>9218004.04</t>
   </si>
   <si>
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 4142.25</t>
+    <t>4142.25</t>
   </si>
   <si>
     <t>EEF(NI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 7131965.42</t>
+    <t>7131965.42</t>
   </si>
 </sst>
 </file>
